--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8349514563106796</v>
+        <v>0.8446601941747572</v>
       </c>
       <c r="C14" t="n">
         <v>0.865979381443299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8125</v>
+        <v>0.8303571428571429</v>
       </c>
       <c r="E14" t="n">
         <v>0.8910891089108911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8511299866662174</v>
+        <v>0.8580214568465225</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5992424242424242</v>
+        <v>0.6049242424242425</v>
       </c>
       <c r="C15" t="n">
         <v>0.5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5728260869565217</v>
+        <v>0.5641304347826087</v>
       </c>
       <c r="E15" t="n">
         <v>0.5777153558052435</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5624459667510473</v>
+        <v>0.5616925082530236</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6130386740331492</v>
+        <v>0.6227106227106227</v>
       </c>
       <c r="C16" t="n">
         <v>0.4640883977900552</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5840848806366048</v>
+        <v>0.5722613065326634</v>
       </c>
       <c r="E16" t="n">
         <v>0.6039215686274509</v>
       </c>
       <c r="F16" t="n">
-        <v>0.566283380271815</v>
+        <v>0.565745473915198</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8207262779595558</v>
+        <v>0.8278032646964686</v>
       </c>
       <c r="C17" t="n">
         <v>0.8037819673064874</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7822281167108754</v>
+        <v>0.7858578607322325</v>
       </c>
       <c r="E17" t="n">
         <v>0.8610366919044846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8169432634703508</v>
+        <v>0.8196199461599183</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6238636363636363</v>
+        <v>0.6261363636363636</v>
       </c>
       <c r="C18" t="n">
         <v>0.603021978021978</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5788043478260869</v>
+        <v>0.5635869565217391</v>
       </c>
       <c r="E18" t="n">
         <v>0.6853932584269664</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6227708051596669</v>
+        <v>0.6195346391517618</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[82, 6], [11, 4]]</t>
+          <t>[[83, 5], [11, 4]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[87, 5], [16, 4]]</t>
+          <t>[[90, 2], [17, 3]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[85, 3], [12, 2]]</t>
+          <t>[[86, 2], [13, 2]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8511299866662174</v>
+        <v>0.8580214568465225</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0298799961935556</v>
+        <v>0.02291634670723615</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5624459667510473</v>
+        <v>0.5616925082530236</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03739779132835293</v>
+        <v>0.03852798834433759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.566283380271815</v>
+        <v>0.565745473915198</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05992369851963366</v>
+        <v>0.06139841118827034</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8169432634703508</v>
+        <v>0.8196199461599183</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02888296539894429</v>
+        <v>0.02816484296480621</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6227708051596669</v>
+        <v>0.6195346391517618</v>
       </c>
       <c r="O4" t="n">
-        <v>0.039515286526341</v>
+        <v>0.04411278632172243</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[85, 3], [12, 2]]</t>
+          <t>[[86, 2], [13, 2]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -613,16 +613,16 @@
         <v>0.7669902912621359</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7319587628865979</v>
+        <v>0.7731958762886598</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6875</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="E8" t="n">
         <v>0.7821782178217822</v>
       </c>
       <c r="F8" t="n">
-        <v>0.742156817992629</v>
+        <v>0.7725553820574302</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.7806818181818183</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6826923076923077</v>
+        <v>0.6414835164835164</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7315217391304347</v>
+        <v>0.7217391304347827</v>
       </c>
       <c r="E9" t="n">
         <v>0.7322097378277153</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7317764007080689</v>
+        <v>0.7190285507319583</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.6740506329113924</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6049498746867168</v>
+        <v>0.6077205882352942</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6273410019963875</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="E10" t="n">
         <v>0.6434531450577663</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6374486636630657</v>
+        <v>0.6499107427139039</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.7974069067223792</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7689068030901998</v>
+        <v>0.7942086112795634</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7235953988021676</v>
+        <v>0.7865448504983388</v>
       </c>
       <c r="E11" t="n">
         <v>0.8130060117693413</v>
       </c>
       <c r="F11" t="n">
-        <v>0.775728780096022</v>
+        <v>0.7977915950674056</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.8492424242424242</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8021978021978022</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8521739130434782</v>
+        <v>0.8244565217391304</v>
       </c>
       <c r="E12" t="n">
         <v>0.752808988764045</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8058640238201791</v>
+        <v>0.8071764342358505</v>
       </c>
     </row>
     <row r="13">
@@ -726,12 +726,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[63, 21], [5, 8]]</t>
+          <t>[[69, 15], [7, 6]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[61, 31], [4, 16]]</t>
+          <t>[[73, 19], [7, 13]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[66, 23], [4, 11]]</t>
+          <t>[[70, 18], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742156817992629</v>
+        <v>0.7725553820574302</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03643412521228306</v>
+        <v>0.006042617151345017</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7317764007080689</v>
+        <v>0.7190285507319583</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03464549277698324</v>
+        <v>0.04998862035357322</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6374486636630657</v>
+        <v>0.6499107427139039</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02516989302208123</v>
+        <v>0.02740930178744094</v>
       </c>
       <c r="L3" t="n">
-        <v>0.775728780096022</v>
+        <v>0.7977915950674056</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03399986025946677</v>
+        <v>0.009630076543422598</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8058640238201791</v>
+        <v>0.8071764342358505</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04523030938896783</v>
+        <v>0.03552729529338744</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[66, 23], [4, 11]]</t>
+          <t>[[70, 18], [5, 10]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.883495145631068</v>
+        <v>0.8640776699029126</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.8350515463917526</v>
       </c>
       <c r="D2" t="n">
         <v>0.8214285714285714</v>
       </c>
       <c r="E2" t="n">
-        <v>0.900990099009901</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8576640210276943</v>
+        <v>0.8504364766337794</v>
       </c>
     </row>
     <row r="3">
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7382575757575758</v>
+        <v>0.7268939393939393</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6062271062271063</v>
+        <v>0.6121794871794872</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6173913043478261</v>
+        <v>0.6369565217391304</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7275280898876404</v>
+        <v>0.7162921348314606</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6723510190550371</v>
+        <v>0.6730805207860044</v>
       </c>
     </row>
     <row r="4">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7520064205457464</v>
+        <v>0.7268939393939393</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6097041420118343</v>
+        <v>0.6196078431372549</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6354166666666667</v>
+        <v>0.653250773993808</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7449494949494949</v>
+        <v>0.7162921348314606</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6855191810434356</v>
+        <v>0.6790111728391157</v>
       </c>
     </row>
     <row r="5">
@@ -534,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8799887796287926</v>
+        <v>0.8640776699029126</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8217556274019399</v>
+        <v>0.8291489791793005</v>
       </c>
       <c r="D5" t="n">
-        <v>0.802827380952381</v>
+        <v>0.8084918177797434</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8970397039703971</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8504028729883776</v>
+        <v>0.8457266464184594</v>
       </c>
     </row>
     <row r="6">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9068181818181819</v>
+        <v>0.9015151515151515</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.8498168498168498</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7548913043478261</v>
+        <v>0.7440217391304348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7462546816479401</v>
+        <v>0.7855805243445693</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8103243752868203</v>
+        <v>0.8202335662017513</v>
       </c>
     </row>
     <row r="7">
@@ -579,27 +579,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[83, 5], [7, 8]]</t>
+          <t>[[81, 7], [7, 8]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[76, 8], [9, 4]]</t>
+          <t>[[77, 7], [9, 4]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[86, 6], [14, 6]]</t>
+          <t>[[85, 7], [13, 7]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[85, 4], [6, 6]]</t>
+          <t>[[83, 6], [6, 6]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[82, 6], [9, 6]]</t>
+          <t>[[82, 7], [9, 6]]</t>
         </is>
       </c>
     </row>
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7669902912621359</v>
+        <v>0.8155339805825242</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.7525773195876289</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7678571428571429</v>
+        <v>0.7053571428571429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7623762376237624</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7725553820574302</v>
+        <v>0.7589611701627645</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7806818181818183</v>
+        <v>0.781439393939394</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6414835164835164</v>
+        <v>0.6620879120879121</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7217391304347827</v>
+        <v>0.7228260869565217</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7322097378277153</v>
+        <v>0.6849250936329588</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7190285507319583</v>
+        <v>0.7128196216541967</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6740506329113924</v>
+        <v>0.7107169253510717</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6077205882352942</v>
+        <v>0.6072874493927125</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6744186046511628</v>
+        <v>0.6356107660455486</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6434531450577663</v>
+        <v>0.6110397946084724</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6499107427139039</v>
+        <v>0.6411637338494512</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7974069067223792</v>
+        <v>0.8341305548977821</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7942086112795634</v>
+        <v>0.7821278016611711</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7865448504983388</v>
+        <v>0.738095238095238</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8130060117693413</v>
+        <v>0.7960065582938267</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7977915950674056</v>
+        <v>0.7875900382370045</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8492424242424242</v>
+        <v>0.8318181818181818</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8021978021978022</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8244565217391304</v>
+        <v>0.8043478260869565</v>
       </c>
       <c r="E12" t="n">
-        <v>0.752808988764045</v>
+        <v>0.7799625468164794</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8071764342358505</v>
+        <v>0.8004607101089759</v>
       </c>
     </row>
     <row r="13">
@@ -721,27 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[67, 21], [3, 12]]</t>
+          <t>[[73, 15], [4, 11]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[69, 15], [7, 6]]</t>
+          <t>[[66, 18], [6, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[73, 19], [7, 13]]</t>
+          <t>[[64, 28], [5, 15]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[71, 18], [4, 8]]</t>
+          <t>[[70, 19], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[70, 18], [5, 10]]</t>
+          <t>[[68, 20], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="C14" t="n">
         <v>0.865979381443299</v>
@@ -764,7 +764,7 @@
         <v>0.8910891089108911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8580214568465225</v>
+        <v>0.8555942723805031</v>
       </c>
     </row>
     <row r="15">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6049242424242425</v>
+        <v>0.5992424242424242</v>
       </c>
       <c r="C15" t="n">
         <v>0.5</v>
@@ -786,7 +786,7 @@
         <v>0.5777153558052435</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5616925082530236</v>
+        <v>0.5602720537075691</v>
       </c>
     </row>
     <row r="16">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6227106227106227</v>
+        <v>0.6130386740331492</v>
       </c>
       <c r="C16" t="n">
         <v>0.4640883977900552</v>
@@ -808,7 +808,7 @@
         <v>0.6039215686274509</v>
       </c>
       <c r="F16" t="n">
-        <v>0.565745473915198</v>
+        <v>0.5633274867458297</v>
       </c>
     </row>
     <row r="17">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8278032646964686</v>
+        <v>0.8207262779595558</v>
       </c>
       <c r="C17" t="n">
         <v>0.8037819673064874</v>
@@ -830,7 +830,7 @@
         <v>0.8610366919044846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8196199461599183</v>
+        <v>0.8178506994756901</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6261363636363636</v>
+        <v>0.6321969696969696</v>
       </c>
       <c r="C18" t="n">
-        <v>0.603021978021978</v>
+        <v>0.6794871794871795</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5635869565217391</v>
+        <v>0.5654891304347825</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6853932584269664</v>
+        <v>0.6315543071161049</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6195346391517618</v>
+        <v>0.6271818966837591</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[83, 5], [11, 4]]</t>
+          <t>[[82, 6], [11, 4]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6407766990291263</v>
+        <v>0.6504854368932039</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4432989690721649</v>
+        <v>0.4536082474226804</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.6517857142857143</v>
       </c>
       <c r="E20" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8118811881188119</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6366925379588446</v>
+        <v>0.6419401466801027</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6791666666666667</v>
+        <v>0.6848484848484848</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4835164835164835</v>
+        <v>0.4894688644688645</v>
       </c>
       <c r="D21" t="n">
-        <v>0.558695652173913</v>
+        <v>0.5532608695652175</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6713483146067416</v>
+        <v>0.7130149812734082</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5981817792409512</v>
+        <v>0.6101483000389938</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5605903378300473</v>
+        <v>0.5680335507921714</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3886554621848739</v>
+        <v>0.3958161946174639</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5363834422657952</v>
+        <v>0.5300699300699301</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6286764705882353</v>
+        <v>0.6559081943697328</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5285764282172378</v>
+        <v>0.5374569674623245</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6936268007285191</v>
+        <v>0.7017888326894018</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5224378411158278</v>
+        <v>0.5325907195898096</v>
       </c>
       <c r="D23" t="n">
-        <v>0.690725178960473</v>
+        <v>0.6838161838161838</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8220733838089691</v>
+        <v>0.8325246725856018</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6822158011534473</v>
+        <v>0.6876801021702492</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7946969696969697</v>
+        <v>0.7931818181818181</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4496336996336997</v>
+        <v>0.4972527472527473</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5951086956521739</v>
+        <v>0.6038043478260868</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7780898876404494</v>
+        <v>0.7893258426966292</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6543823131558231</v>
+        <v>0.6708911889893203</v>
       </c>
     </row>
     <row r="25">
@@ -1005,22 +1005,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[55, 33], [4, 11]]</t>
+          <t>[[56, 32], [4, 11]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[36, 48], [6, 7]]</t>
+          <t>[[37, 47], [6, 7]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[66, 26], [12, 8]]</t>
+          <t>[[65, 27], [12, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[75, 14], [6, 6]]</t>
+          <t>[[75, 14], [5, 7]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1042,13 +1042,13 @@
         <v>0.8865979381443299</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8811881188118812</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8821554254734494</v>
+        <v>0.8868628158553448</v>
       </c>
     </row>
     <row r="27">
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7276515151515152</v>
+        <v>0.7</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.6094322344322345</v>
       </c>
       <c r="D27" t="n">
-        <v>0.575</v>
+        <v>0.6</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5720973782771536</v>
+        <v>0.5777153558052435</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6129179925879364</v>
+        <v>0.6217868975593694</v>
       </c>
     </row>
     <row r="28">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7797576621525303</v>
+        <v>0.7613899613899614</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6026070763500931</v>
+        <v>0.6453971419076105</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5881462253947654</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="E28" t="n">
-        <v>0.592741935483871</v>
+        <v>0.6039215686274509</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6408132248453149</v>
+        <v>0.6593438346479225</v>
       </c>
     </row>
     <row r="29">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9009957857296086</v>
+        <v>0.8960227911684222</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8485016030255909</v>
+        <v>0.8594628485676989</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7985383640802201</v>
+        <v>0.8152380952380953</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8540402427339507</v>
+        <v>0.8610366919044846</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8505189988923425</v>
+        <v>0.8579401067196754</v>
       </c>
     </row>
     <row r="30">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9121212121212121</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7710622710622711</v>
+        <v>0.7655677655677655</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7630434782608695</v>
+        <v>0.7418478260869564</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7659176029962547</v>
+        <v>0.7827715355805243</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8030361411101519</v>
+        <v>0.8017134484754782</v>
       </c>
     </row>
     <row r="31">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[87, 1], [8, 7]]</t>
+          <t>[[88, 0], [9, 6]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[84, 0], [11, 2]]</t>
+          <t>[[83, 1], [10, 3]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[92, 0], [17, 3]]</t>
+          <t>[[92, 0], [16, 4]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[87, 2], [10, 2]]</t>
+          <t>[[88, 1], [10, 2]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[88, 1], [12, 4]]</t>
+          <t>[[88, 0], [11, 4]]</t>
         </is>
       </c>
     </row>
@@ -1290,38 +1290,38 @@
         <v>413</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8576640210276943</v>
+        <v>0.8504364766337794</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03514699723641821</v>
+        <v>0.02350478830686535</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6723510190550371</v>
+        <v>0.6730805207860044</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0607888259683161</v>
+        <v>0.04943937401547219</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6855191810434356</v>
+        <v>0.6790111728391157</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06366061835595054</v>
+        <v>0.04437055101177949</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8504028729883776</v>
+        <v>0.8457266464184594</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03916124358960546</v>
+        <v>0.0285286154679963</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8103243752868203</v>
+        <v>0.8202335662017513</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06522694582380344</v>
+        <v>0.06018916571114516</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[[82, 6], [9, 6]]</t>
+          <t>[[82, 7], [9, 6]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7725553820574302</v>
+        <v>0.7589611701627645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006042617151345017</v>
+        <v>0.03913531287756854</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7190285507319583</v>
+        <v>0.7128196216541967</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04998862035357322</v>
+        <v>0.04516805714596446</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6499107427139039</v>
+        <v>0.6411637338494512</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02740930178744094</v>
+        <v>0.04160389484014787</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7977915950674056</v>
+        <v>0.7875900382370045</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009630076543422598</v>
+        <v>0.03433813030146948</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8071764342358505</v>
+        <v>0.8004607101089759</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03552729529338744</v>
+        <v>0.02022394888130213</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[70, 18], [5, 10]]</t>
+          <t>[[68, 20], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -1406,34 +1406,34 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8580214568465225</v>
+        <v>0.8555942723805031</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02291634670723615</v>
+        <v>0.02465143237439031</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5616925082530236</v>
+        <v>0.5602720537075691</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03852798834433759</v>
+        <v>0.03698163777587113</v>
       </c>
       <c r="J4" t="n">
-        <v>0.565745473915198</v>
+        <v>0.5633274867458297</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06139841118827034</v>
+        <v>0.05926063520179829</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8196199461599183</v>
+        <v>0.8178506994756901</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02816484296480621</v>
+        <v>0.02781532783102874</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6195346391517618</v>
+        <v>0.6271818966837591</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04411278632172243</v>
+        <v>0.0405774227462556</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1464,34 +1464,34 @@
         <v>413</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6366925379588446</v>
+        <v>0.6419401466801027</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1277838094126439</v>
+        <v>0.1270027746050099</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5981817792409512</v>
+        <v>0.6101483000389938</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08157692407035703</v>
+        <v>0.09214306489664385</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5285764282172378</v>
+        <v>0.5374569674623245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08758386708629183</v>
+        <v>0.09365134470140224</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6822158011534473</v>
+        <v>0.6876801021702492</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1064093045297194</v>
+        <v>0.1063563024812105</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6543823131558231</v>
+        <v>0.6708911889893203</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1417983808937271</v>
+        <v>0.1261276316802085</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1522,38 +1522,38 @@
         <v>413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8821554254734494</v>
+        <v>0.8868628158553448</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02291749161890257</v>
+        <v>0.01977820906644485</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6129179925879364</v>
+        <v>0.6217868975593694</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06626370022149397</v>
+        <v>0.04660176174840839</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6408132248453149</v>
+        <v>0.6593438346479225</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08038956420682584</v>
+        <v>0.06071932785276048</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8505189988923425</v>
+        <v>0.8579401067196754</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03628485031373729</v>
+        <v>0.0286603394167721</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8030361411101519</v>
+        <v>0.8017134484754782</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06304577709255402</v>
+        <v>0.06794012358956417</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[[88, 1], [12, 4]]</t>
+          <t>[[88, 0], [11, 4]]</t>
         </is>
       </c>
     </row>
